--- a/tests/workbooktests/workbooks/test_optimizers.xlsx
+++ b/tests/workbooktests/workbooks/test_optimizers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52281D79-9129-4901-99CF-F7A11B5E3468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEB04A8-1A27-4C47-970E-26DE8CB0033D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="-19695" windowWidth="21330" windowHeight="15900" activeTab="1" xr2:uid="{E76B3670-D287-482D-903A-DB7A1E5EF242}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" activeTab="1" xr2:uid="{E76B3670-D287-482D-903A-DB7A1E5EF242}"/>
   </bookViews>
   <sheets>
     <sheet name="Constraints" sheetId="1" r:id="rId1"/>
@@ -553,18 +553,18 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2">_xll.qlNoConstraint()</f>
-        <v>⚡[Book1]Constraints!R2C2NoConstraint,A</v>
+      <c r="B2" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlNoConstraint()</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="str" cm="1">
-        <f t="array" ref="B3">_xll.qlPositiveConstraint()</f>
-        <v>⚡[Book1]Constraints!R3C2PositiveConstraint,A</v>
+      <c r="B3" t="e" cm="1">
+        <f t="array" aca="1" ref="B3" ca="1">_xll.qlPositiveConstraint()</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -603,27 +603,27 @@
       <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="str" cm="1">
-        <f t="array" ref="B10">_xll.qlBoundaryConstraint(A6,B6)</f>
-        <v>⚡[test_optimizers.xlsx]Constraints!R10C2BoundaryConstraint,A</v>
+      <c r="B10" t="e" cm="1">
+        <f t="array" aca="1" ref="B10" ca="1">_xll.qlBoundaryConstraint(A6,B6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="str" cm="1">
-        <f t="array" ref="B11">_xll.qlCompositeConstraint(B3,B10)</f>
-        <v>⚡[test_optimizers.xlsx]Constraints!R11C2CompositeConstraint,A</v>
+      <c r="B11" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlCompositeConstraint(B3,B10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
-      <c r="B12" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlNonhomogeneousBoundaryConstraint(A6:A8,B6:B8)</f>
-        <v>⚡[test_optimizers.xlsx]Constraints!R12C2NonhomogeneousBoundaryConstraint,A</v>
+      <c r="B12" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlNonhomogeneousBoundaryConstraint(A6:A8,B6:B8)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -698,9 +698,9 @@
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlEndCriteria(B2,B3,B4,B5,B6)</f>
-        <v>⚡[Book1]EndCriteria!R8C2EndCriteria,A</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlEndCriteria(B2,B3,B4,B5,B6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -715,63 +715,63 @@
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="b" cm="1">
-        <f t="array" ref="B11">_xll.qlEndCriteriaSucceded($B$8,A11)</f>
-        <v>0</v>
+      <c r="B11" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlEndCriteriaSucceded($B$8,A11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="b" cm="1">
-        <f t="array" ref="B12">_xll.qlEndCriteriaSucceded($B$8,A12)</f>
-        <v>0</v>
+      <c r="B12" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlEndCriteriaSucceded($B$8,A12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="b" cm="1">
-        <f t="array" ref="B13">_xll.qlEndCriteriaSucceded($B$8,A13)</f>
-        <v>1</v>
+      <c r="B13" t="e" cm="1">
+        <f t="array" aca="1" ref="B13" ca="1">_xll.qlEndCriteriaSucceded($B$8,A13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="b" cm="1">
-        <f t="array" ref="B14">_xll.qlEndCriteriaSucceded($B$8,A14)</f>
-        <v>1</v>
+      <c r="B14" t="e" cm="1">
+        <f t="array" aca="1" ref="B14" ca="1">_xll.qlEndCriteriaSucceded($B$8,A14)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" t="b" cm="1">
-        <f t="array" ref="B15">_xll.qlEndCriteriaSucceded($B$8,A15)</f>
-        <v>1</v>
+      <c r="B15" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlEndCriteriaSucceded($B$8,A15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
-      <c r="B16" t="b" cm="1">
-        <f t="array" ref="B16">_xll.qlEndCriteriaSucceded($B$8,A16)</f>
-        <v>0</v>
+      <c r="B16" t="e" cm="1">
+        <f t="array" aca="1" ref="B16" ca="1">_xll.qlEndCriteriaSucceded($B$8,A16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" t="b" cm="1">
-        <f t="array" ref="B17">_xll.qlEndCriteriaSucceded($B$8,A17)</f>
-        <v>0</v>
+      <c r="B17" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlEndCriteriaSucceded($B$8,A17)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -822,18 +822,18 @@
       <c r="A24" t="s">
         <v>35</v>
       </c>
-      <c r="B24" t="str" cm="1">
-        <f t="array" ref="B24">_xll.qlLevenbergMarquardt()</f>
-        <v>⚡[test_optimizers.xlsx]EndCriteria!R24C2LevenbergMarquardt,A</v>
+      <c r="B24" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlLevenbergMarquardt()</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>35</v>
       </c>
-      <c r="B25" t="str" cm="1">
-        <f t="array" ref="B25">_xll.qlLevenbergMarquardt(B19,B20,B21,B22)</f>
-        <v>⚡[test_optimizers.xlsx]EndCriteria!R25C2LevenbergMarquardt,A</v>
+      <c r="B25" t="e" cm="1">
+        <f t="array" aca="1" ref="B25" ca="1">_xll.qlLevenbergMarquardt(B19,B20,B21,B22)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
